--- a/stories/arbres/ATOM-FAM.VER.001-09.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Garance est dans la cuisine. Papa coupe une poire. Ça sent le fruit. Garance veut aider. Elle touche le saladier. Le saladier glisse. La farine tombe. Le sol est blanc. Garance a le ventre serré. Elle va vers papa. Garance dit : papa, la farine est tombée. Papa s'approche. Papa dit : merci de raconter. On ramasse ensemble. Garance prend la balayette. Papa tient la pelle. Maman entre. Garance dit : maman, j'ai raconté. La farine est tombée. Maman écoute. Maman dit : merci Garance. On raconte à papa ou maman. C'est comme ça.</t>
+          <t>Garance est dans la cuisine. Papa coupe une poire. Ça sent le fruit. Garance veut aider. Elle touche le saladier. Le saladier glisse. La farine tombe. Le sol est blanc. Garance a le ventre serré. Elle va vers papa. Papa, la farine est tombée. Papa s'approche. Merci de raconter. On ramasse ensemble. Garance prend la balayette. Papa tient la pelle. Maman entre. Maman, j'ai raconté. La farine est tombée. Maman écoute. Merci Garance. On raconte à papa ou maman. C'est comme ça.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Garance est dans la cuisine. Papa coupe une poire. Ça sent le fruit. Garance veut aider. Elle touche le saladier. Le saladier glisse. La farine tombe. Le sol est blanc. Garance a le ventre serré. Elle va vers papa.
+enfant-f|Papa, la farine est tombée. Papa s'approche.
+papa|Merci de raconter. On ramasse ensemble.
+narrateur|Garance prend la balayette. Papa tient la pelle. Maman entre.
+enfant-f|Maman, j'ai raconté.
+narrateur|La farine est tombée. Maman écoute.
+maman|Merci Garance. On raconte à papa ou maman. C'est comme ça.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|La farine est tombée. Que fait Garance ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Garance a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Raconter aide.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le sol est propre. Garance se lave les mains. Papa range la pelle.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-09.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-09.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 maman|Merci Garance. On raconte à papa ou maman. C'est comme ça.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|La farine est tombée. Que fait Garance ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Garance a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Raconter aide.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Le sol est propre. Garance se lave les mains. Papa range la pelle.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.VER.001-09.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Garance raconte la farine</t>
+          <t>Mila raconte la farine</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un rayon tient de la poussière blanche. Le saladier glisse. Mila raconte la farine. Papa et maman ramassent avec elle.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Garance est dans la cuisine. Papa coupe une poire. Ça sent le fruit. Garance veut aider. Elle touche le saladier. Le saladier glisse. La farine tombe. Le sol est blanc. Garance a le ventre serré. Elle va vers papa. Papa, la farine est tombée. Papa s'approche. Merci de raconter. On ramasse ensemble. Garance prend la balayette. Papa tient la pelle. Maman entre. Maman, j'ai raconté. La farine est tombée. Maman écoute. Merci Garance. On raconte à papa ou maman. C'est comme ça.</t>
+          <t>Un rayon tient de la poussière blanche. Les grains dansent, tout petits. Une poire attend sur la planche. Elle sent le fruit mûr. La peau est jaune et douce. Papa prépare la poire. Les morceaux sont jaunes. Maman casse un œuf dans un bol. Le saladier est sur la table. Il est large et blanc. Mila, tu sens la poire ? Oui, papa. Ça sent doux. On fait un gâteau. La farine est déjà là. En ce moment, Mila veut aider. Elle touche le bord du saladier. Le saladier glisse. La farine tombe. Le sol devient blanc. Ça fait un nuage tout léger. Mila a le ventre serré. Elle va vers papa. Papa, la farine est tombée. Merci de raconter. On ramasse ensemble. Mila prend la balayette. Le bois est lisse. Papa tient la pelle. La farine revient dans le seau. Parce qu'elle a raconté, papa peut aider. Maman s'approche. Ça sent la poire, ici. Maman, j'ai raconté. La farine est tombée. Merci, Mila. On raconte à papa ou maman. C'est comme ça. Bravo, Mila. Tu as fait du bon travail. Le sol redevient clair. Le rayon n'a plus de nuage. La poire attend encore. On reprend le saladier ? Oui, maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,53 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Garance est dans la cuisine. Papa coupe une poire. Ça sent le fruit. Garance veut aider. Elle touche le saladier. Le saladier glisse. La farine tombe. Le sol est blanc. Garance a le ventre serré. Elle va vers papa.
-enfant-f|Papa, la farine est tombée. Papa s'approche.
-papa|Merci de raconter. On ramasse ensemble.
-narrateur|Garance prend la balayette. Papa tient la pelle. Maman entre.
+          <t>narrateur|Un rayon tient de la poussière blanche.
+narrateur|Les grains dansent, tout petits.
+narrateur|Une poire attend sur la planche.
+narrateur|Elle sent le fruit mûr.
+narrateur|La peau est jaune et douce.
+narrateur|Papa prépare la poire.
+narrateur|Les morceaux sont jaunes.
+narrateur|Maman casse un œuf dans un bol.
+narrateur|Le saladier est sur la table.
+narrateur|Il est large et blanc.
+papa|Mila, tu sens la poire ?
+enfant-f|Oui, papa.
+enfant-f|Ça sent doux.
+maman|On fait un gâteau.
+papa|La farine est déjà là.
+narrateur|En ce moment, Mila veut aider.
+narrateur|Elle touche le bord du saladier.
+narrateur|Le saladier glisse.
+narrateur|La farine tombe.
+narrateur|Le sol devient blanc.
+narrateur|Ça fait un nuage tout léger.
+narrateur|Mila a le ventre serré.
+narrateur|Elle va vers papa.
+enfant-f|Papa, la farine est tombée.
+papa|Merci de raconter.
+papa|On ramasse ensemble.
+narrateur|Mila prend la balayette.
+narrateur|Le bois est lisse.
+narrateur|Papa tient la pelle.
+narrateur|La farine revient dans le seau.
+narrateur|Parce qu'elle a raconté, papa peut aider.
+narrateur|Maman s'approche.
+maman|Ça sent la poire, ici.
 enfant-f|Maman, j'ai raconté.
-narrateur|La farine est tombée. Maman écoute.
-maman|Merci Garance. On raconte à papa ou maman. C'est comme ça.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-f|La farine est tombée.
+maman|Merci, Mila.
+maman|On raconte à papa ou maman.
+maman|C'est comme ça.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Le sol redevient clair.
+narrateur|Le rayon n'a plus de nuage.
+narrateur|La poire attend encore.
+maman|On reprend le saladier ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1395,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>La farine est tombée. Que fait Garance ?</t>
+          <t>La farine est tombée. Que fait Mila ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,10 +1551,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|La farine est tombée. Que fait Garance ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|La farine est tombée.
+narrateur|Que fait Mila ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1530,7 +1579,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Garance a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Raconter aide.</t>
+          <t>Mila a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Tu as dit ce qui s'est passé ? Oui, papa. Bravo. Raconter aide. La balayette repose près du seau. Il reste un peu de farine sur le bois. Mila souffle. Le ventre se desserre. Le saladier est prêt ? Oui. Le saladier est de nouveau stable.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,10 +1723,23 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Garance a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Raconter aide.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Mila a raconté.
+narrateur|Papa a écouté.
+narrateur|Maman a écouté.
+narrateur|Ensemble, ils ont ramassé.
+papa|Tu as dit ce qui s'est passé ?
+enfant-f|Oui, papa.
+maman|Bravo.
+maman|Raconter aide.
+narrateur|La balayette repose près du seau.
+narrateur|Il reste un peu de farine sur le bois.
+narrateur|Mila souffle.
+narrateur|Le ventre se desserre.
+papa|Le saladier est prêt ?
+enfant-f|Oui.
+narrateur|Le saladier est de nouveau stable.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1702,7 +1764,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le sol est propre. Garance se lave les mains. Papa range la pelle.</t>
+          <t>Le sol est propre. On se lave les mains ? Oui, papa. Mila se lave les mains. L'eau emporte la farine. Tu as fini tes mains ? Oui. Bravo. Papa range la pelle. Maman pose la poire dans un bol. Les morceaux sont prêts. Ils sentent bon.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,10 +1904,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le sol est propre. Garance se lave les mains. Papa range la pelle.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le sol est propre.
+papa|On se lave les mains ?
+enfant-f|Oui, papa.
+narrateur|Mila se lave les mains.
+narrateur|L'eau emporte la farine.
+papa|Tu as fini tes mains ?
+enfant-f|Oui.
+papa|Bravo.
+narrateur|Papa range la pelle.
+narrateur|Maman pose la poire dans un bol.
+maman|Les morceaux sont prêts.
+enfant-f|Ils sentent bon.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1870,7 +1942,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le saladier est de nouveau sur la table. Merci d'avoir raconté. On raconte à papa ou maman. Oui. Le rayon est calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,10 +2082,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le saladier est de nouveau sur la table.
+maman|Merci d'avoir raconté.
+papa|On raconte à papa ou maman.
+enfant-f|Oui.
+narrateur|Le rayon est calme.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2146,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-09.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-09.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un rayon tient de la poussière blanche. Les grains dansent, tout petits. Une poire attend sur la planche. Elle sent le fruit mûr. La peau est jaune et douce. Papa prépare la poire. Les morceaux sont jaunes. Maman casse un œuf dans un bol. Le saladier est sur la table. Il est large et blanc. Mila, tu sens la poire ? Oui, papa. Ça sent doux. On fait un gâteau. La farine est déjà là. En ce moment, Mila veut aider. Elle touche le bord du saladier. Le saladier glisse. La farine tombe. Le sol devient blanc. Ça fait un nuage tout léger. Mila a le ventre serré. Elle va vers papa. Papa, la farine est tombée. Merci de raconter. On ramasse ensemble. Mila prend la balayette. Le bois est lisse. Papa tient la pelle. La farine revient dans le seau. Parce qu'elle a raconté, papa peut aider. Maman s'approche. Ça sent la poire, ici. Maman, j'ai raconté. La farine est tombée. Merci, Mila. On raconte à papa ou maman. C'est comme ça. Bravo, Mila. Tu as fait du bon travail. Le sol redevient clair. Le rayon n'a plus de nuage. La poire attend encore. On reprend le saladier ? Oui, maman.</t>
+          <t>Un rayon tient de la poussière blanche. Les grains dansent, tout petits. Une poire attend sur la planche. Elle sent le fruit mûr. La peau est jaune et douce. Un bol en bois attend aussi. La cuillère tape un petit coup. Papa prépare la poire. Les morceaux sont jaunes. Maman casse un œuf dans un bol. Le saladier est sur la table. Il est large et blanc. Mila, tu sens la poire ? Oui, papa. Ça sent doux. On fait un gâteau. La farine est déjà là. En ce moment, Mila veut aider. Elle touche le bord du saladier. Le saladier glisse. La farine tombe. Le sol devient blanc. Ça fait un nuage tout léger. Mila a le ventre serré. Elle va vers papa. Papa, la farine est tombée. Merci de raconter. On ramasse ensemble. Mila prend la balayette. Le bois est lisse. Papa tient la pelle. La farine revient dans le seau. Parce qu'elle a raconté, papa peut aider. Maman s'approche. Ça sent la poire, ici. Maman, j'ai raconté. La farine est tombée. Merci, Mila. On raconte à papa ou maman. C'est comme ça. Bravo, Mila. Le sol redevient clair. Le rayon n'a plus de nuage. La poire attend encore. On reprend le saladier ? Oui, maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Garance est dans la cuisine. Papa coupe une poire. Ça sent le fruit. Garance veut aider. Elle touche le saladier. Le saladier glisse. La farine tombe. Le sol est blanc. Garance a le ventre serré. Elle va vers papa. Garance dit : papa, la farine est tombée. Papa s'approche. Papa dit : merci de &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt;. On ramasse ensemble. Garance prend la balayette. Papa tient la pelle. Maman entre. Garance dit : maman, j'ai raconté. La farine est tombée. Maman écoute. Maman dit : merci Garance. On raconte à papa ou maman. C'est comme ça.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un rayon tient de la poussière blanche. Les grains dansent, tout petits. Une poire attend sur la planche. Elle sent le fruit mûr. La peau est jaune et douce. Un bol en bois attend aussi. La cuillère tape un petit coup. Papa prépare la poire. Les morceaux sont jaunes. Maman casse un œuf dans un bol. Le saladier est sur la table. Il est large et blanc. Mila, tu sens la poire ? Oui, papa. Ça sent doux. On fait un gâteau. La farine est déjà là. En ce moment, Mila veut aider. Elle touche le bord du saladier. Le saladier glisse. La farine tombe. Le sol devient blanc. Ça fait un nuage tout léger. Mila a le ventre serré. Elle va vers papa. Papa, la farine est tombée. Merci de raconter. On ramasse ensemble. Mila prend la balayette. Le bois est lisse. Papa tient la pelle. La farine revient dans le seau. Parce qu'elle a raconté, papa peut aider. Maman s'approche. Ça sent la poire, ici. Maman, j'ai raconté. La farine est tombée. Merci, Mila. On raconte à papa ou maman. C'est comme ça. Bravo, Mila. Le sol redevient clair. Le rayon n'a plus de nuage. La poire attend encore. On reprend le saladier ? Oui, maman.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1329,6 +1329,8 @@
 narrateur|Une poire attend sur la planche.
 narrateur|Elle sent le fruit mûr.
 narrateur|La peau est jaune et douce.
+narrateur|Un bol en bois attend aussi.
+narrateur|La cuillère tape un petit coup.
 narrateur|Papa prépare la poire.
 narrateur|Les morceaux sont jaunes.
 narrateur|Maman casse un œuf dans un bol.
@@ -1363,7 +1365,6 @@
 maman|On raconte à papa ou maman.
 maman|C'est comme ça.
 papa|Bravo, Mila.
-papa|Tu as fait du bon travail.
 narrateur|Le sol redevient clair.
 narrateur|Le rayon n'a plus de nuage.
 narrateur|La poire attend encore.
@@ -1400,7 +1401,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;La farine est tombée. Que fait Garance ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La farine est tombée. Que fait Mila ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1579,12 +1580,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Tu as dit ce qui s'est passé ? Oui, papa. Bravo. Raconter aide. La balayette repose près du seau. Il reste un peu de farine sur le bois. Mila souffle. Le ventre se desserre. Le saladier est prêt ? Oui. Le saladier est de nouveau stable.</t>
+          <t>Mila a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Tu as dit ce qui s'est passé ? Oui, papa. Bravo. Raconter aide. La balayette repose près du seau. Il reste un peu de farine sur le bois. Mila souffle. Le ventre se desserre. Le saladier est prêt ? Oui. Le saladier est de nouveau stable. On remet un peu de farine ? Oui, maman. Papa verse tout doux, cette fois.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Garance a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt; aide.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Tu as dit ce qui s'est passé ? Oui, papa. Bravo. Raconter aide. La balayette repose près du seau. Il reste un peu de farine sur le bois. Mila souffle. Le ventre se desserre. Le saladier est prêt ? Oui. Le saladier est de nouveau stable. On remet un peu de farine ? Oui, maman. Papa verse tout doux, cette fois.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1737,7 +1738,10 @@
 narrateur|Le ventre se desserre.
 papa|Le saladier est prêt ?
 enfant-f|Oui.
-narrateur|Le saladier est de nouveau stable.</t>
+narrateur|Le saladier est de nouveau stable.
+maman|On remet un peu de farine ?
+enfant-f|Oui, maman.
+narrateur|Papa verse tout doux, cette fois.</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1773,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le sol est propre. Garance se lave les mains. &lt;emphasis level="moderate"&gt;papa&lt;/emphasis&gt; range la pelle.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le sol est propre. On se lave les mains ? Oui, papa. Mila se lave les mains. L'eau emporte la farine. Tu as fini tes mains ? Oui. Bravo. Papa range la pelle. Maman pose la poire dans un bol. Les morceaux sont prêts. Ils sentent bon.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1942,12 +1946,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le saladier est de nouveau sur la table. Merci d'avoir raconté. On raconte à papa ou maman. Oui. Le rayon est calme. L'histoire est finie.</t>
+          <t>Le saladier est de nouveau sur la table. Merci d'avoir raconté. On raconte à papa ou maman. Oui. Le rayon est calme. La poire brille encore. On peut continuer le gâteau.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le saladier est de nouveau sur la table. Merci d'avoir raconté. On raconte à papa ou maman. Oui. Le rayon est calme. La poire brille encore. On peut continuer le gâteau.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2087,7 +2091,8 @@
 papa|On raconte à papa ou maman.
 enfant-f|Oui.
 narrateur|Le rayon est calme.
-narrateur|L'histoire est finie.</t>
+narrateur|La poire brille encore.
+maman|On peut continuer le gâteau.</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2153,6 +2158,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-09.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-09.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>cuisine, rayon de soleil, poire et farine</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Garance, papa, maman</t>
+          <t>Mila, papa, maman</t>
         </is>
       </c>
     </row>
